--- a/pasto_case/results/AHP_results/AHP_TOPSIS_results3.xlsx
+++ b/pasto_case/results/AHP_results/AHP_TOPSIS_results3.xlsx
@@ -478,249 +478,249 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03637404313781585</v>
+        <v>0.03638757697915165</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01804090330844417</v>
+        <v>0.01800928308966843</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002800572280295448</v>
+        <v>0.002560345135496554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001578696652489231</v>
+        <v>6.149147643547424e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003600769080489672</v>
+        <v>0.006832288454621097</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09192698054366501</v>
+        <v>0.09458602483005739</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02238272085671223</v>
+        <v>0.02243752709391093</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1958077099538147</v>
+        <v>0.1917351398502148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01431659201035889</v>
+        <v>0.01419271840412553</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01646587413622039</v>
+        <v>0.0163581564444181</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007803732221950978</v>
+        <v>0.009366410885919529</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00670370233357376</v>
+        <v>0.006032497491785243</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07168241805744628</v>
+        <v>0.0982891104325448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03678098488620998</v>
+        <v>0.02779568109303689</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06861450114035032</v>
+        <v>0.09191852376635974</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6510193531728584</v>
+        <v>0.7678163495661798</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03485290075511543</v>
+        <v>0.03484258258585265</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01646587413622039</v>
+        <v>0.0163581564444181</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007803732221950978</v>
+        <v>0.009366410885919529</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00670370233357376</v>
+        <v>0.006032497491785243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07168241805744628</v>
+        <v>0.0982891104325448</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02943166916348277</v>
+        <v>0.01673064872725892</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07162185241669682</v>
+        <v>0.09420951067758827</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7087516723488889</v>
+        <v>0.8491921336961057</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03587635230928941</v>
+        <v>0.03592147959928673</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01646587413622039</v>
+        <v>0.0163581564444181</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007552542929935011</v>
+        <v>0.008888072294127827</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00670370233357376</v>
+        <v>0.006032497491785243</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07168241805744628</v>
+        <v>0.0982891104325448</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0295817041392978</v>
+        <v>0.01713763834604959</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07190495564660147</v>
+        <v>0.09441859813859864</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7085163291243927</v>
+        <v>0.8463766895864403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0328214995787109</v>
+        <v>0.03288877904064891</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01423892451979365</v>
+        <v>0.01471825362693543</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02965334979485032</v>
+        <v>0.02593788445249702</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001794998688364916</v>
+        <v>0.003042009293596539</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01034859430105724</v>
+        <v>0.01463623290067785</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08124382012585979</v>
+        <v>0.08384652557403274</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03334241444474428</v>
+        <v>0.03107791922278608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.290980976639038</v>
+        <v>0.2704204425588518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0332308128415696</v>
+        <v>0.0332141391556886</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01755766344540398</v>
+        <v>0.01751614484108425</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004054579132831799</v>
+        <v>0.00388618106450589</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004252277889298665</v>
+        <v>0.004539938592281121</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09127429273887028</v>
+        <v>0.06216121437252106</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02591892699219415</v>
+        <v>0.04247853343209122</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08985402183695598</v>
+        <v>0.0587600801170552</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7761227708690089</v>
+        <v>0.5804117426848209</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03632690061731694</v>
+        <v>0.03633715738456299</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01755766344540398</v>
+        <v>0.01751614484108425</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004054579132831799</v>
+        <v>0.00388618106450589</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004252277889298665</v>
+        <v>0.004539938592281121</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09127429273887028</v>
+        <v>0.06216121437252106</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0257206378296529</v>
+        <v>0.0423554661505708</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09055634254759791</v>
+        <v>0.05984403684339042</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7787985399500015</v>
+        <v>0.585560938069596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03643248653650628</v>
+        <v>0.03644715463736623</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01755766344540398</v>
+        <v>0.01751614484108425</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004054579132831799</v>
+        <v>0.00388618106450589</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004252277889298665</v>
+        <v>0.004539938592281121</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09127429273887028</v>
+        <v>0.06216121437252106</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02572042110809698</v>
+        <v>0.04235532331875799</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09058206379474931</v>
+        <v>0.05988482695987463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7788489117013911</v>
+        <v>0.5857271022848847</v>
       </c>
     </row>
   </sheetData>
